--- a/pdf2img/tabel/table_10.xlsx
+++ b/pdf2img/tabel/table_10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,15 @@
       </c>
       <c r="K1" t="n">
         <v>10</v>
+      </c>
+      <c r="L1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -479,16 +488,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Per,3</t>
+          <t>[Per31]Desember;2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1|</t>
+          <t>dan'31/Desember;2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -500,24 +512,31 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Desember,2025</t>
+          <t>{</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dan'3</t>
+          <t>dafam</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1|Desember,2024</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Jutaan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ruplah)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -525,28 +544,27 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{</t>
+          <t>l.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dafam</t>
+          <t>|TAGIHAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jutaan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ruplah)</t>
-        </is>
-      </c>
+          <t>KOMITMEN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -554,89 +572,153 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>|.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>|TAGIHAN</t>
+          <t>Fasilitas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KOMITMEN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>pinjaman/pembiayaan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>belum</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ditarik</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fasilitas</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>pinjaman/pembiayaan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>belum</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ditarik</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Posisi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>valas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>yang</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>akan</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>diterima</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>dari</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>transaksi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>spof</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>derivatif/</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4.024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -646,72 +728,46 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Posisi</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>valas</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>akan</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>diterima</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>dari</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>transaksi</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>spof</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>derivatif/forward</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.024</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+          <t>IIl.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IKEWAJIBAN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>KOMITMEN</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -720,37 +776,71 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fasilitas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>kredit/pembiayaan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>belum</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ditarik</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>Committed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -758,16 +848,31 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>;</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Uncommitted</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.485.629</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.129.909</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
@@ -775,72 +880,133 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Il.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>|KEWAJIBAN</t>
+          <t>Irrevocable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KOMITMEN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+          <t>LIC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>masih</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>berjalan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>22.091</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>277.816</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fasilitas</t>
+          <t>Posisi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kredit/pembiayaan</t>
+          <t>valas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>belum</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ditarik</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>akan</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>diserahkan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>untuk</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>fransaksi</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>spot</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>derivatif/forward</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -850,15 +1016,26 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Committed</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>IIl.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[TAGIHAN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KONTINJENSI</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -867,16 +1044,31 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Garansi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>diterima</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -884,16 +1076,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -905,28 +1100,27 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b.</t>
+          <t>[V.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Uncommitted</t>
+          <t>[KEWAJIBAN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.485.629</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>4.129.909</t>
-        </is>
-      </c>
+          <t>KONTINJENSI</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -934,55 +1128,61 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>trrevocable</t>
+          <t>Garansi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LIC</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>masih</t>
+          <t>diberikan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>berjalan</t>
+          <t>479.926</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22.091</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>277.816</t>
-        </is>
-      </c>
+          <t>231.933</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -992,332 +1192,33 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3,</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Posisi</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>valas</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>akan</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>diserahkan</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>untuk</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>transaksi</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>spot</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>derivatif/forward</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>4.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>|TAGIHAN</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>KONTINJENSI</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>lil.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Garansi</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>diterima</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>IV.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>|]KEWAJIBAN</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>KONTINJENSI</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Garansi</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>diberikan</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>479,926</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>231.933</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
